--- a/docs/BOM_raw.xlsx
+++ b/docs/BOM_raw.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3230DF25-6BC2-4714-B659-4A6200472906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2C7DEF-01F7-4C8B-869A-79BDB6DA1FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs/BOM_raw.xlsx
+++ b/docs/BOM_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2C7DEF-01F7-4C8B-869A-79BDB6DA1FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92CD478-5864-43F4-810A-2EDAFEBE0C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -833,7 +833,7 @@
         <f>C18*D18</f>
         <v>6.14</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1254,8 +1254,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" display="https://www.aliexpress.com/ssr/300000512/BundleDeals2?spm=a2g0o.productlist.main.12.4bad23b2W0Z283&amp;productIds=1005007345095808:12000040354473755&amp;pha_manifest=ssr&amp;_immersiveMode=true&amp;disableNav=YES&amp;sourceName=SEARCHProduct&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007345095808%7C_p_origin_prod%3A1005006953448721&amp;pvid=fead97a0-7013-472f-8f48-f34087dd6ca8" xr:uid="{8188D1EC-FE01-445E-8168-1909B737FBEE}"/>
+    <hyperlink ref="G18" r:id="rId2" xr:uid="{0B2CAFBD-B1C0-49B8-AA67-4397D28F333F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>